--- a/HGA/MASTER GAMBAR.xlsx
+++ b/HGA/MASTER GAMBAR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD HGA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E936E89-239F-4164-94EE-D252F57DDE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D559DB-B86C-413D-A2D5-31BDD7641FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3ADC970B-AF40-422A-B8D9-698DD6F80022}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="52">
   <si>
     <t>Tipe Motor</t>
   </si>
@@ -192,10 +192,7 @@
     <t>https://github.com/suwandakurnia/gambar-aksesoris/blob/main/VARIO%20160/eCatalog%20Honda%20Collection%20update%20Apr%2025_page-0078.jpg?raw=true</t>
   </si>
   <si>
-    <t>2025 ADV 160</t>
-  </si>
-  <si>
-    <t>2025 VARIO 125</t>
+    <t>SCOOPY</t>
   </si>
 </sst>
 </file>
@@ -211,18 +208,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -237,9 +228,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -258,7 +248,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2CF655CC-DB9D-4F68-8848-80A6D7A123D4}" name="MASTER_GAMBAR" displayName="MASTER_GAMBAR" ref="A1:B55" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2CF655CC-DB9D-4F68-8848-80A6D7A123D4}" name="MASTER_GAMBAR" displayName="MASTER_GAMBAR" ref="A1:B38" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{E28232FD-98C6-47A9-9CF0-6586A8D0937F}" name="Tipe Motor"/>
     <tableColumn id="2" xr3:uid="{81C0F3E3-6113-4540-9D59-9FA742ED74E8}" name="Url"/>
@@ -584,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61716D0B-BA11-4E2A-9264-78BF1D4FB5E3}">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
@@ -753,282 +743,146 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>14</v>
-      </c>
-      <c r="B42" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>14</v>
-      </c>
-      <c r="B43" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>14</v>
-      </c>
-      <c r="B44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>14</v>
-      </c>
-      <c r="B45" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>16</v>
-      </c>
-      <c r="B51" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>16</v>
-      </c>
-      <c r="B52" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>16</v>
-      </c>
-      <c r="B53" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
